--- a/data/trans_orig/P19C04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85673</t>
+          <t>86666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118635</t>
+          <t>121847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>58160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90194</t>
+          <t>88476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153160</t>
+          <t>152978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201628</t>
+          <t>201507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359202</t>
+          <t>355990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392164</t>
+          <t>391171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447910</t>
+          <t>449628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>478729</t>
+          <t>479944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>814313</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862781</t>
+          <t>862963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129452</t>
+          <t>129194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172568</t>
+          <t>173717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80080</t>
+          <t>79984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117745</t>
+          <t>117767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220135</t>
+          <t>221736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>279681</t>
+          <t>276794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549560</t>
+          <t>548411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>592676</t>
+          <t>592934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686481</t>
+          <t>686459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>724146</t>
+          <t>724242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1246673</t>
+          <t>1249560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1306219</t>
+          <t>1304618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90520</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127900</t>
+          <t>128008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84404</t>
+          <t>84717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122655</t>
+          <t>121329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239487</t>
+          <t>235179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417189</t>
+          <t>417081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>455231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461954</t>
+          <t>463280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>500205</t>
+          <t>499892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>890211</t>
+          <t>894519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942846</t>
+          <t>945107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110387</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150481</t>
+          <t>147620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108918</t>
+          <t>109544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151677</t>
+          <t>150974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228044</t>
+          <t>230043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287134</t>
+          <t>287594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>562068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>599301</t>
+          <t>601284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662321</t>
+          <t>663024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705080</t>
+          <t>704454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1236552</t>
+          <t>1236092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1295642</t>
+          <t>1293643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>450878</t>
+          <t>449175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>531386</t>
+          <t>530224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>364094</t>
+          <t>368865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>437561</t>
+          <t>439813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>834415</t>
+          <t>838333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>948895</t>
+          <t>946159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1923356</t>
+          <t>1924518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2003864</t>
+          <t>2005567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2303376</t>
+          <t>2301124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2376843</t>
+          <t>2372072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4246784</t>
+          <t>4249520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4361264</t>
+          <t>4357346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>164074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209873</t>
+          <t>210547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>92441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133089</t>
+          <t>132134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269650</t>
+          <t>267999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330011</t>
+          <t>331416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396078</t>
+          <t>395404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>440737</t>
+          <t>441877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502712</t>
+          <t>503667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>541857</t>
+          <t>543360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>911741</t>
+          <t>910336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>972102</t>
+          <t>973753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202161</t>
+          <t>204173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>256049</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150868</t>
+          <t>153503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201985</t>
+          <t>199541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>363745</t>
+          <t>364095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>441838</t>
+          <t>440725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>610949</t>
+          <t>611602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>664837</t>
+          <t>662825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>694745</t>
+          <t>697189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>745862</t>
+          <t>743227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1321890</t>
+          <t>1323003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1399983</t>
+          <t>1399633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132107</t>
+          <t>135093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179993</t>
+          <t>182575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87650</t>
+          <t>88726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126737</t>
+          <t>130074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238220</t>
+          <t>235465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295826</t>
+          <t>295256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>456040</t>
+          <t>453458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503926</t>
+          <t>500940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551760</t>
+          <t>548423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>590847</t>
+          <t>589771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1018703</t>
+          <t>1019273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076309</t>
+          <t>1079064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>128035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172992</t>
+          <t>175596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135666</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182837</t>
+          <t>181449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275926</t>
+          <t>274396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>340307</t>
+          <t>338254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632684</t>
+          <t>630080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>677641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>751356</t>
+          <t>752744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>798527</t>
+          <t>798083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1399562</t>
+          <t>1401615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1463943</t>
+          <t>1465473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>672392</t>
+          <t>676315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>772075</t>
+          <t>774731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>509695</t>
+          <t>507321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>593783</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1210693</t>
+          <t>1204086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1340636</t>
+          <t>1338789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2142584</t>
+          <t>2139928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2242267</t>
+          <t>2238344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2551438</t>
+          <t>2552889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2635526</t>
+          <t>2637900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4719243</t>
+          <t>4721090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4849186</t>
+          <t>4855793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95574</t>
+          <t>95870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135148</t>
+          <t>132758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99163</t>
+          <t>97496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>170526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220259</t>
+          <t>221791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389845</t>
+          <t>392235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429419</t>
+          <t>429123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445200</t>
+          <t>446867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>481005</t>
+          <t>478480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849097</t>
+          <t>847565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>898488</t>
+          <t>898830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109186</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152458</t>
+          <t>154636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92925</t>
+          <t>93261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133532</t>
+          <t>133933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215350</t>
+          <t>214802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274562</t>
+          <t>277279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>663888</t>
+          <t>661710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>707160</t>
+          <t>706381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>732841</t>
+          <t>732440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773448</t>
+          <t>773112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1408157</t>
+          <t>1405440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1467369</t>
+          <t>1467917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85522</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123902</t>
+          <t>126272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>52309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84306</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148184</t>
+          <t>147707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195224</t>
+          <t>201456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426458</t>
+          <t>424088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464838</t>
+          <t>462346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495432</t>
+          <t>496172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527323</t>
+          <t>527429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934874</t>
+          <t>928642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>981914</t>
+          <t>982391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106234</t>
+          <t>106515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94436</t>
+          <t>94122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133856</t>
+          <t>136015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212067</t>
+          <t>210912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269727</t>
+          <t>267544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626510</t>
+          <t>625696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>666401</t>
+          <t>666120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741891</t>
+          <t>739732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781311</t>
+          <t>781625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1378655</t>
+          <t>1380838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1436315</t>
+          <t>1437470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>436630</t>
+          <t>437264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>518235</t>
+          <t>516550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +6014,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>373344</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>333507</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>410704</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>849072</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>796671</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>906223</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>373344</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>335473</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>413296</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>849072</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>794359</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>903583</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2146098</t>
+          <t>2147783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2227703</t>
+          <t>2227069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,82 +6127,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2492877</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2455517</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2532714</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4681482</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4624331</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4733883</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>84,65%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>83,61%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2381</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2492877</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2452925</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2530748</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>4681482</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4626971</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4736195</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>83,66%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115921</t>
+          <t>116290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159807</t>
+          <t>159647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88757</t>
+          <t>88147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114461</t>
+          <t>115059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213705</t>
+          <t>213962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262925</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451497</t>
+          <t>451657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495383</t>
+          <t>495014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>537071</t>
+          <t>536473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>562775</t>
+          <t>563385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>999911</t>
+          <t>998133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1049131</t>
+          <t>1048874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69425</t>
+          <t>69541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169732</t>
+          <t>171943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97645</t>
+          <t>96604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130184</t>
+          <t>128545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>149109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283022</t>
+          <t>282768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996984</t>
+          <t>994773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1097291</t>
+          <t>1097175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>812141</t>
+          <t>813780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>844680</t>
+          <t>845721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1826018</t>
+          <t>1826272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1943449</t>
+          <t>1959931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>59183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95825</t>
+          <t>93362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84535</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>85135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164519</t>
+          <t>165607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590442</t>
+          <t>592905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626725</t>
+          <t>627084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>837518</t>
+          <t>837869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894030</t>
+          <t>892924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1443801</t>
+          <t>1442713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530134</t>
+          <t>1523185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121794</t>
+          <t>121367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167144</t>
+          <t>168263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82338</t>
+          <t>81866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122931</t>
+          <t>120974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211253</t>
+          <t>214605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274843</t>
+          <t>279588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>721694</t>
+          <t>720575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767044</t>
+          <t>767471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>939986</t>
+          <t>941943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>980579</t>
+          <t>981051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1676912</t>
+          <t>1672167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1740502</t>
+          <t>1737150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>374856</t>
+          <t>376258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>544619</t>
+          <t>540180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308764</t>
+          <t>305337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417583</t>
+          <t>415367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>745530</t>
+          <t>757706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>940970</t>
+          <t>944760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2808506</t>
+          <t>2812945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2978269</t>
+          <t>2976867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3161244</t>
+          <t>3163460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3270063</t>
+          <t>3273490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5990982</t>
+          <t>5987192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6186422</t>
+          <t>6174246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86666</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121847</t>
+          <t>121011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58160</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88476</t>
+          <t>89414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152978</t>
+          <t>153491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201507</t>
+          <t>199000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355990</t>
+          <t>356826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391171</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449628</t>
+          <t>448690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>479944</t>
+          <t>480097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>816941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862963</t>
+          <t>862450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129194</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173717</t>
+          <t>172467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79984</t>
+          <t>80521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117767</t>
+          <t>118169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221736</t>
+          <t>221806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276794</t>
+          <t>278979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>548411</t>
+          <t>549661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>592934</t>
+          <t>594032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686459</t>
+          <t>686057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>724242</t>
+          <t>723705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1249560</t>
+          <t>1247375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1304618</t>
+          <t>1304548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>91478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128008</t>
+          <t>128622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84717</t>
+          <t>84285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121329</t>
+          <t>120890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184591</t>
+          <t>188047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235179</t>
+          <t>241276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417081</t>
+          <t>416467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455231</t>
+          <t>453611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463280</t>
+          <t>463719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>499892</t>
+          <t>500324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>894519</t>
+          <t>888422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>945107</t>
+          <t>941651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>109495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147620</t>
+          <t>148770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109544</t>
+          <t>110258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150974</t>
+          <t>150655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230043</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287594</t>
+          <t>286411</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562068</t>
+          <t>560918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601284</t>
+          <t>600193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>663024</t>
+          <t>663343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>704454</t>
+          <t>703740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1236092</t>
+          <t>1237275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293643</t>
+          <t>1295200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>449175</t>
+          <t>452315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>530224</t>
+          <t>532460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368865</t>
+          <t>368079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>439813</t>
+          <t>443924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>838333</t>
+          <t>838459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>946159</t>
+          <t>950149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1924518</t>
+          <t>1922282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2005567</t>
+          <t>2002427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2301124</t>
+          <t>2297013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2372072</t>
+          <t>2372858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4249520</t>
+          <t>4245530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4357346</t>
+          <t>4357220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164074</t>
+          <t>164101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210547</t>
+          <t>210072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92441</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132134</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267999</t>
+          <t>268598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>331416</t>
+          <t>331670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395404</t>
+          <t>395879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>441877</t>
+          <t>441850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>503667</t>
+          <t>503652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>543360</t>
+          <t>542405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>910336</t>
+          <t>910082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>973753</t>
+          <t>973154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204173</t>
+          <t>201571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255396</t>
+          <t>253885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153503</t>
+          <t>151448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199541</t>
+          <t>200168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364095</t>
+          <t>369185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>440725</t>
+          <t>440556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>611602</t>
+          <t>613113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>662825</t>
+          <t>665427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697189</t>
+          <t>696562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>743227</t>
+          <t>745282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1323003</t>
+          <t>1323172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1399633</t>
+          <t>1394543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135093</t>
+          <t>136641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182575</t>
+          <t>180951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88726</t>
+          <t>88446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130074</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235465</t>
+          <t>230883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295256</t>
+          <t>293314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453458</t>
+          <t>455082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500940</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548423</t>
+          <t>549292</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>589771</t>
+          <t>590051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1019273</t>
+          <t>1021215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1079064</t>
+          <t>1083646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128035</t>
+          <t>127343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175596</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181449</t>
+          <t>182513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274396</t>
+          <t>272741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>338254</t>
+          <t>336956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630080</t>
+          <t>632969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>677641</t>
+          <t>678333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752744</t>
+          <t>751680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>798083</t>
+          <t>797808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1401615</t>
+          <t>1402913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1465473</t>
+          <t>1467128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>676315</t>
+          <t>669120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>774731</t>
+          <t>766749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507321</t>
+          <t>512065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>603803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1204086</t>
+          <t>1206019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1338789</t>
+          <t>1337771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2139928</t>
+          <t>2147910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2238344</t>
+          <t>2245539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2552889</t>
+          <t>2541418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2637900</t>
+          <t>2633156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4721090</t>
+          <t>4722108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4855793</t>
+          <t>4853860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95870</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132758</t>
+          <t>135289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65883</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>98691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170526</t>
+          <t>169017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221791</t>
+          <t>220191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392235</t>
+          <t>389704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429123</t>
+          <t>429499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446867</t>
+          <t>445672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>478480</t>
+          <t>478927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>847565</t>
+          <t>849165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>898830</t>
+          <t>900339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109965</t>
+          <t>111101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154636</t>
+          <t>153228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93261</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133933</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>214802</t>
+          <t>214254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277279</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661710</t>
+          <t>663118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>705245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>732440</t>
+          <t>732160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773112</t>
+          <t>772969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1405440</t>
+          <t>1404909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1467917</t>
+          <t>1468465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88014</t>
+          <t>88316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126272</t>
+          <t>124915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52309</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147707</t>
+          <t>147843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201456</t>
+          <t>196380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424088</t>
+          <t>425445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462346</t>
+          <t>462044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496172</t>
+          <t>495603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527429</t>
+          <t>527773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>928642</t>
+          <t>933718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>982391</t>
+          <t>982255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106515</t>
+          <t>107069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146939</t>
+          <t>146454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>93191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136015</t>
+          <t>136276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210912</t>
+          <t>212306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267544</t>
+          <t>268702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625696</t>
+          <t>626181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>666120</t>
+          <t>665566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739732</t>
+          <t>739471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781625</t>
+          <t>782556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1380838</t>
+          <t>1379680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437470</t>
+          <t>1436076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>437264</t>
+          <t>439636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>516550</t>
+          <t>519767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>333507</t>
+          <t>337268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>410704</t>
+          <t>413031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>796671</t>
+          <t>790208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>906223</t>
+          <t>899820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2147783</t>
+          <t>2144566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2227069</t>
+          <t>2224697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2455517</t>
+          <t>2453190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2532714</t>
+          <t>2528953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4624331</t>
+          <t>4630734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4733883</t>
+          <t>4740346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>137010</t>
+          <t>148971</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116290</t>
+          <t>128741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159647</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>107869</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88147</t>
+          <t>93487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>123117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>237960</t>
+          <t>256840</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213962</t>
+          <t>230863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264703</t>
+          <t>284536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>474294</t>
+          <t>510560</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451657</t>
+          <t>486048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495014</t>
+          <t>530790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>550582</t>
+          <t>598280</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>536473</t>
+          <t>583032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563385</t>
+          <t>612662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1024876</t>
+          <t>1108840</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>998133</t>
+          <t>1081144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1048874</t>
+          <t>1134817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128954</t>
+          <t>150425</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69541</t>
+          <t>126943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171943</t>
+          <t>175358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>111968</t>
+          <t>127498</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96604</t>
+          <t>110994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128545</t>
+          <t>147075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>277923</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149109</t>
+          <t>247679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282768</t>
+          <t>307021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1037762</t>
+          <t>865755</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994773</t>
+          <t>840822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1097175</t>
+          <t>889237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>830357</t>
+          <t>920286</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>813780</t>
+          <t>900709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>845721</t>
+          <t>936790</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1868118</t>
+          <t>1786041</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1826272</t>
+          <t>1756943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1959931</t>
+          <t>1816285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>72406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93362</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>69830</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29129</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84184</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135508</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85135</t>
+          <t>139193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165607</t>
+          <t>186807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>611135</t>
+          <t>682298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592905</t>
+          <t>658334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627084</t>
+          <t>701602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>861677</t>
+          <t>725515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>837869</t>
+          <t>709529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>892924</t>
+          <t>739350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1472812</t>
+          <t>1407812</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1442713</t>
+          <t>1382546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523185</t>
+          <t>1430160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>143882</t>
+          <t>164811</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121367</t>
+          <t>140975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168263</t>
+          <t>189172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>103107</t>
+          <t>111918</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81866</t>
+          <t>96830</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120974</t>
+          <t>129497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>246989</t>
+          <t>276729</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214605</t>
+          <t>247879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279588</t>
+          <t>305627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>744956</t>
+          <t>781949</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>720575</t>
+          <t>757588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767471</t>
+          <t>805785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>959810</t>
+          <t>964252</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941943</t>
+          <t>946673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>981051</t>
+          <t>979340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1704766</t>
+          <t>1746201</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1672167</t>
+          <t>1717303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1737150</t>
+          <t>1775051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>376258</t>
+          <t>503648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>540180</t>
+          <t>599034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>305337</t>
+          <t>388067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>415367</t>
+          <t>448988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>757706</t>
+          <t>916155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>944760</t>
+          <t>1027041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2868148</t>
+          <t>2840562</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2812945</t>
+          <t>2797445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2976867</t>
+          <t>2892831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3202425</t>
+          <t>3208332</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3163460</t>
+          <t>3176460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3273490</t>
+          <t>3237381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6070573</t>
+          <t>6048894</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5987192</t>
+          <t>5994885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6174246</t>
+          <t>6105771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
